--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487477_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487477_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. CHOITHRAMANI BLANCO</t>
+          <t>L. MC-CARTHY SANTOS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,40 +565,40 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5353</v>
+        <v>2.5254</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3466</v>
+        <v>0.588</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1887</v>
+        <v>1.9373</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.5292</v>
+        <v>-3.0588</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.1811</v>
+        <v>-3.9086</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3482</v>
+        <v>0.8498</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.9469</v>
+        <v>-2.2202</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.9614</v>
+        <v>-3.0285</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0145</v>
+        <v>0.8083</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.5823</v>
+        <v>-0.8386</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.2197</v>
+        <v>-0.8801</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3626</v>
+        <v>0.0415</v>
       </c>
       <c r="P2" t="n">
         <v>0.3917</v>
@@ -610,28 +610,28 @@
         <v>1.3709</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8479</v>
+        <v>0.2685</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4478</v>
+        <v>0.1953</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4001</v>
+        <v>0.0732</v>
       </c>
       <c r="V2" t="n">
-        <v>1.8249</v>
+        <v>4.924</v>
       </c>
       <c r="W2" t="n">
-        <v>1.8249</v>
+        <v>3.5922</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.3318</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. MC-CARTHY SANTOS</t>
+          <t>A. GARRIDO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.444</v>
+        <v>0.7571</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.333</v>
+        <v>1.4206</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7769</v>
+        <v>-0.6635</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.0588</v>
+        <v>1.8251</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.9086</v>
+        <v>1.6634</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8498</v>
+        <v>0.1617</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.2202</v>
+        <v>3.4074</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.0285</v>
+        <v>3.0196</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8083</v>
+        <v>0.3878</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8386</v>
+        <v>-1.5823</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8801</v>
+        <v>-1.3562</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0415</v>
+        <v>-0.2262</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3917</v>
+        <v>0.1958</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3709</v>
+        <v>1.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8129</v>
+        <v>-0.598</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7258</v>
+        <v>-0.3417</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0872</v>
+        <v>-0.2563</v>
       </c>
       <c r="V3" t="n">
-        <v>4.924</v>
+        <v>-0.6659</v>
       </c>
       <c r="W3" t="n">
-        <v>3.5922</v>
+        <v>-0.6659</v>
       </c>
       <c r="X3" t="n">
-        <v>1.3318</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5718</v>
+        <v>0.7335</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1529</v>
+        <v>0.3146</v>
       </c>
       <c r="F4" t="n">
         <v>0.4189</v>
@@ -766,10 +766,10 @@
         <v>0.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5875</v>
+        <v>-0.4258</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5346</v>
+        <v>-0.3729</v>
       </c>
       <c r="U4" t="n">
         <v>-0.0529</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. GARRIDO RODRIGUEZ</t>
+          <t>R. CHOITHRAMANI BLANCO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.0428</v>
+        <v>0.6573</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2355</v>
+        <v>0.7092000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2783</v>
+        <v>-0.0518</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8251</v>
+        <v>-2.5292</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6634</v>
+        <v>-2.1811</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1617</v>
+        <v>-0.3482</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4074</v>
+        <v>-0.9469</v>
       </c>
       <c r="K5" t="n">
-        <v>3.0196</v>
+        <v>-0.9614</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3878</v>
+        <v>0.0145</v>
       </c>
       <c r="M5" t="n">
         <v>-1.5823</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3562</v>
+        <v>-1.2197</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2262</v>
+        <v>-0.3626</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1958</v>
+        <v>0.3917</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1751</v>
+        <v>1.3709</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.3979</v>
+        <v>0.97</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.5268</v>
+        <v>0.8104</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8711</v>
+        <v>0.1595</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6659</v>
+        <v>1.8249</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6659</v>
+        <v>1.8249</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.5787</v>
+        <v>-1.4437</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1808</v>
+        <v>-1.019</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.398</v>
+        <v>-0.4247</v>
       </c>
       <c r="G6" t="n">
         <v>0.3936</v>
@@ -922,13 +922,13 @@
         <v>0.5875</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3052</v>
+        <v>-1.1702</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7128</v>
+        <v>-0.5511</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5924</v>
+        <v>-0.6192</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2754</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. KOUROUMA</t>
+          <t>I. OKEKE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8047</v>
+        <v>-4.0968</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8786</v>
+        <v>-0.3281</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9261</v>
+        <v>-3.7687</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.9326</v>
+        <v>-1.1408</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.0038</v>
+        <v>-0.9595</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9288</v>
+        <v>-0.1813</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.1378</v>
+        <v>0.7883</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.2591</v>
+        <v>0.7383</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1212</v>
+        <v>0.0501</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7948</v>
+        <v>-1.9292</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7447</v>
+        <v>-1.6978</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0501</v>
+        <v>-0.2314</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9792</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9792</v>
+        <v>1.3709</v>
       </c>
       <c r="S7" t="n">
-        <v>4.4378</v>
+        <v>-0.8764999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>3.6647</v>
+        <v>-0.6499</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7731</v>
+        <v>-0.2266</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.3306</v>
+        <v>-1.492</v>
       </c>
       <c r="W7" t="n">
-        <v>-1.4469</v>
+        <v>1.492</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8837</v>
+        <v>-2.9839</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. OKEKE</t>
+          <t>O. KOUROUMA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.5785</v>
+        <v>-4.1897</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.1038</v>
+        <v>-3.13</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.4747</v>
+        <v>-1.0597</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1408</v>
+        <v>-2.9326</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9595</v>
+        <v>-2.0038</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1813</v>
+        <v>-0.9288</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7883</v>
+        <v>-1.1378</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7383</v>
+        <v>-1.2591</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0501</v>
+        <v>0.1212</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.9292</v>
+        <v>-1.7948</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6978</v>
+        <v>-0.7447</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2314</v>
+        <v>-1.0501</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5875</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3709</v>
+        <v>0.9792</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3582</v>
+        <v>2.0527</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.4256</v>
+        <v>1.4133</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0675</v>
+        <v>0.6395</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.492</v>
+        <v>-2.3306</v>
       </c>
       <c r="W8" t="n">
-        <v>1.492</v>
+        <v>-1.4469</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.9839</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-7.1643</v>
+        <v>-6.264</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.3645</v>
+        <v>-4.3841</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7998</v>
+        <v>-1.88</v>
       </c>
       <c r="G9" t="n">
         <v>-4.4493</v>
@@ -1156,13 +1156,13 @@
         <v>0.5875</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7357</v>
+        <v>0.1645</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7546</v>
+        <v>0.2258</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0189</v>
+        <v>-0.0613</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6083</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-11.6179</v>
+        <v>-11.3209</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.1257</v>
+        <v>-5.8288</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.492399999999999</v>
+        <v>-5.4922</v>
       </c>
       <c r="G10" t="n">
         <v>-11.1244</v>
@@ -1210,7 +1210,7 @@
         <v>-1.5618</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.817400000000001</v>
+        <v>-4.8174</v>
       </c>
       <c r="L10" t="n">
         <v>3.2554</v>
@@ -1219,7 +1219,7 @@
         <v>-9.5627</v>
       </c>
       <c r="N10" t="n">
-        <v>-7.1193</v>
+        <v>-7.119300000000001</v>
       </c>
       <c r="O10" t="n">
         <v>-2.4435</v>
@@ -1234,16 +1234,16 @@
         <v>7.8337</v>
       </c>
       <c r="S10" t="n">
-        <v>0.08830000000000027</v>
+        <v>0.3852000000000002</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4322999999999997</v>
+        <v>0.7292</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.344</v>
+        <v>-0.3441000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>1.376700000000001</v>
+        <v>1.3767</v>
       </c>
       <c r="W10" t="n">
         <v>4.7963</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>7.9131</v>
+        <v>6.556</v>
       </c>
       <c r="E11" t="n">
-        <v>7.7515</v>
+        <v>6.4211</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1617</v>
+        <v>0.1349</v>
       </c>
       <c r="G11" t="n">
         <v>3.1116</v>
@@ -1312,13 +1312,13 @@
         <v>1.1751</v>
       </c>
       <c r="S11" t="n">
-        <v>2.9487</v>
+        <v>1.5916</v>
       </c>
       <c r="T11" t="n">
-        <v>2.4013</v>
+        <v>1.071</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5474</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>1.0694</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.5677</v>
+        <v>3.9844</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6528</v>
+        <v>1.9598</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9148</v>
+        <v>2.0246</v>
       </c>
       <c r="G12" t="n">
         <v>2.6365</v>
@@ -1390,13 +1390,13 @@
         <v>0.9792</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6552</v>
+        <v>-1.2385</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.891</v>
+        <v>-0.584</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7642</v>
+        <v>-0.6544</v>
       </c>
       <c r="V12" t="n">
         <v>1.6071</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.6903</v>
+        <v>3.9662</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7968</v>
+        <v>1.6155</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8935</v>
+        <v>2.3507</v>
       </c>
       <c r="G13" t="n">
         <v>1.8291</v>
@@ -1468,13 +1468,13 @@
         <v>0.9792</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4718</v>
+        <v>-0.1958</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9504</v>
+        <v>-0.1317</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5213</v>
+        <v>-0.0641</v>
       </c>
       <c r="V13" t="n">
         <v>1.5495</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. OLOWOKERE</t>
+          <t>A. FILGUEIRA BUCETA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4156</v>
+        <v>1.3938</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4575</v>
+        <v>-0.1601</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8731</v>
+        <v>1.5539</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.8419</v>
+        <v>1.5663</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0987</v>
+        <v>0.6972</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9407</v>
+        <v>0.8691</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.318</v>
+        <v>0.1269</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5018</v>
+        <v>-0.6006</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.8198</v>
+        <v>0.7275</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.524</v>
+        <v>1.4394</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4031</v>
+        <v>1.2978</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1209</v>
+        <v>0.1416</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7834</v>
+        <v>0.5875</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.3917</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1751</v>
+        <v>0.5875</v>
       </c>
       <c r="S14" t="n">
-        <v>2.505</v>
+        <v>-0.4848</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9181</v>
+        <v>-0.287</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5869</v>
+        <v>-0.1978</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.0309</v>
+        <v>-0.2754</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.6659</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.365</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2738</v>
+        <v>1.0027</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3664</v>
+        <v>-0.1453</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9075</v>
+        <v>1.148</v>
       </c>
       <c r="G15" t="n">
         <v>1.2893</v>
@@ -1624,13 +1624,13 @@
         <v>1.5668</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8956</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7399</v>
+        <v>0.2282</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1557</v>
+        <v>0.3963</v>
       </c>
       <c r="V15" t="n">
         <v>0.8516</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. FILGUEIRA BUCETA</t>
+          <t>H. REY PEREZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0305</v>
+        <v>0.4028</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4671</v>
+        <v>0.4953</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4976</v>
+        <v>-0.0925</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5663</v>
+        <v>2.3787</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6972</v>
+        <v>1.0657</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8691</v>
+        <v>1.3129</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1269</v>
+        <v>1.7527</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6006</v>
+        <v>0.0408</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7275</v>
+        <v>1.7119</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4394</v>
+        <v>0.626</v>
       </c>
       <c r="N16" t="n">
-        <v>1.2978</v>
+        <v>1.0249</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1416</v>
+        <v>-0.399</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5875</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R16" t="n">
         <v>0.5875</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.848</v>
+        <v>-0.7581</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.594</v>
+        <v>-0.2782</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.254</v>
+        <v>-0.4799</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2754</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2754</v>
+        <v>-0.8260999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H. REY PEREZ</t>
+          <t>M. OLOWOKERE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4664</v>
+        <v>0.2089</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8023</v>
+        <v>-0.9691</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3359</v>
+        <v>1.1781</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3787</v>
+        <v>-0.8419</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0657</v>
+        <v>0.0987</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3129</v>
+        <v>-0.9407</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7527</v>
+        <v>-0.318</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0408</v>
+        <v>0.5018</v>
       </c>
       <c r="L17" t="n">
-        <v>1.7119</v>
+        <v>-0.8198</v>
       </c>
       <c r="M17" t="n">
-        <v>0.626</v>
+        <v>-0.524</v>
       </c>
       <c r="N17" t="n">
-        <v>1.0249</v>
+        <v>-0.4031</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.399</v>
+        <v>-0.1209</v>
       </c>
       <c r="P17" t="n">
+        <v>0.7834</v>
+      </c>
+      <c r="Q17" t="n">
         <v>-0.3917</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-0.9792</v>
-      </c>
       <c r="R17" t="n">
-        <v>0.5875</v>
+        <v>1.1751</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6945</v>
+        <v>1.2983</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0288</v>
+        <v>0.4064</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7233000000000001</v>
+        <v>0.8919</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-1.0309</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.365</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3482</v>
+        <v>-0.3039</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5013</v>
+        <v>0.706</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8495</v>
+        <v>-1.0099</v>
       </c>
       <c r="G18" t="n">
         <v>-0.5181</v>
@@ -1858,13 +1858,13 @@
         <v>0.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2495</v>
+        <v>0.2938</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1476</v>
+        <v>0.3523</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1019</v>
+        <v>-0.0585</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2754</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5522</v>
+        <v>-1.0626</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5891999999999999</v>
+        <v>-0.1798</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.963</v>
+        <v>-0.8828</v>
       </c>
       <c r="G19" t="n">
         <v>-0.4501</v>
@@ -1936,13 +1936,13 @@
         <v>1.1751</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3264</v>
+        <v>0.8159</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2682</v>
+        <v>0.1411</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5946</v>
+        <v>0.6747</v>
       </c>
       <c r="V19" t="n">
         <v>-2.4077</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.8391</v>
+        <v>-3.8481</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.8651</v>
+        <v>-4.2511</v>
       </c>
       <c r="F20" t="n">
-        <v>0.026</v>
+        <v>0.403</v>
       </c>
       <c r="G20" t="n">
         <v>0.1232</v>
@@ -2014,13 +2014,13 @@
         <v>1.1751</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.3439</v>
+        <v>-1.3529</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.188</v>
+        <v>-0.574</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1559</v>
+        <v>-0.7788</v>
       </c>
       <c r="V20" t="n">
         <v>-1.6392</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>11.6179</v>
+        <v>12.3002</v>
       </c>
       <c r="E21" t="n">
-        <v>5.492199999999999</v>
+        <v>5.492300000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>6.125799999999999</v>
+        <v>6.808</v>
       </c>
       <c r="G21" t="n">
         <v>11.1246</v>
@@ -2062,7 +2062,7 @@
         <v>11.9364</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8121000000000003</v>
+        <v>-0.8121000000000004</v>
       </c>
       <c r="J21" t="n">
         <v>9.562600000000002</v>
@@ -2077,7 +2077,7 @@
         <v>1.5619</v>
       </c>
       <c r="N21" t="n">
-        <v>4.8173</v>
+        <v>4.817299999999999</v>
       </c>
       <c r="O21" t="n">
         <v>-3.2556</v>
@@ -2092,13 +2092,13 @@
         <v>9.792300000000001</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.08820000000000006</v>
+        <v>0.5940000000000003</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3441000000000001</v>
+        <v>0.3441</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4322</v>
+        <v>0.2501000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>-1.3771</v>
